--- a/data/templates/output_test.xlsx
+++ b/data/templates/output_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pfizer-my.sharepoint.com/personal/hoveyo_pfizer_com/Documents/financial-automation-project/data/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_C8B051760544D3645A06C278E3770A51A31B3E2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D819AA31-7B1E-4341-BCD6-B20467D4C47E}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_EC0C1E8184384C310684C86B0F34133B239FBAE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4A491BB-D6A7-484A-B338-D435C25B1738}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" tabRatio="590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Forecast Source Data'!$A$1:$BZ$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Template!$A$14:$BY$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Transactions Source Data'!$A$1:$L$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Transactions Source Data'!$A$1:$AU$56</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="288">
   <si>
     <t xml:space="preserve">Overall Capital </t>
   </si>
@@ -308,6 +308,81 @@
     <t>EXPENSE END</t>
   </si>
   <si>
+    <t>PO #</t>
+  </si>
+  <si>
+    <t>Feb 2025 - FTotal</t>
+  </si>
+  <si>
+    <t>March 2025 - FTotal</t>
+  </si>
+  <si>
+    <t>April 2025 - FTotal</t>
+  </si>
+  <si>
+    <t>May 2025 - FTotal</t>
+  </si>
+  <si>
+    <t>June 2025 - FTotal</t>
+  </si>
+  <si>
+    <t>July 2025 - FTotal</t>
+  </si>
+  <si>
+    <t>Aug 2025 - FTotal</t>
+  </si>
+  <si>
+    <t>Sep 2025 - FTotal</t>
+  </si>
+  <si>
+    <t>Oct 2025 - FTotal</t>
+  </si>
+  <si>
+    <t>Nov 2025 - FTotal</t>
+  </si>
+  <si>
+    <t>Dec 2025 - FTotal</t>
+  </si>
+  <si>
+    <t>Pfizer requested PO</t>
+  </si>
+  <si>
+    <t>IBM PMA</t>
+  </si>
+  <si>
+    <t>PO Owner</t>
+  </si>
+  <si>
+    <t>Work Code</t>
+  </si>
+  <si>
+    <t>Project Name</t>
+  </si>
+  <si>
+    <t>Project Start Date</t>
+  </si>
+  <si>
+    <t>Project End Date</t>
+  </si>
+  <si>
+    <t>Resource Talent Id</t>
+  </si>
+  <si>
+    <t>Resource Name</t>
+  </si>
+  <si>
+    <t>Bill Rate</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Resource Status</t>
+  </si>
+  <si>
+    <t>Forecast Month Hours</t>
+  </si>
+  <si>
     <t>Forecast Fee $</t>
   </si>
   <si>
@@ -317,226 +392,151 @@
     <t>Forecast Total $</t>
   </si>
   <si>
+    <t>Actual Month Hours</t>
+  </si>
+  <si>
+    <t>Acual Fee $</t>
+  </si>
+  <si>
+    <t>Actual Expenses $</t>
+  </si>
+  <si>
+    <t>Actual Total $</t>
+  </si>
+  <si>
+    <t>Monthly Hours Variance</t>
+  </si>
+  <si>
+    <t>Hours Billed Flag</t>
+  </si>
+  <si>
+    <t>Forecast Accuracy</t>
+  </si>
+  <si>
+    <t>Expense%</t>
+  </si>
+  <si>
     <t>Total Forecast Hours 2025</t>
   </si>
   <si>
+    <t>Jan 2025 - FFHours</t>
+  </si>
+  <si>
+    <t>Feb 2025 - FHours</t>
+  </si>
+  <si>
+    <t>March 2025 - FHours</t>
+  </si>
+  <si>
+    <t>April 2025 - FHours</t>
+  </si>
+  <si>
+    <t>May 2025 - FHours</t>
+  </si>
+  <si>
+    <t>June 2025 - FHours</t>
+  </si>
+  <si>
+    <t>July 2025 - FHours</t>
+  </si>
+  <si>
+    <t>Aug 2025 - FHours</t>
+  </si>
+  <si>
+    <t>Sep 2025 - FHours</t>
+  </si>
+  <si>
+    <t>Oct 2025 - FHours</t>
+  </si>
+  <si>
+    <t>Nov 2025 - FHours</t>
+  </si>
+  <si>
+    <t>Dec 2025 - FHours</t>
+  </si>
+  <si>
+    <t>2025 Forecast total Fee</t>
+  </si>
+  <si>
+    <t>Jan 2025 - FFee</t>
+  </si>
+  <si>
+    <t>Feb 2025 - FFee</t>
+  </si>
+  <si>
+    <t>March 2025 - FFee</t>
+  </si>
+  <si>
+    <t>April 2025 - FFee</t>
+  </si>
+  <si>
+    <t>May 2025 - FFee</t>
+  </si>
+  <si>
+    <t>June 2025 - FFee</t>
+  </si>
+  <si>
+    <t>July 2025 - FFee</t>
+  </si>
+  <si>
+    <t>Aug 2025 - FFee</t>
+  </si>
+  <si>
+    <t>Sep 2025 - FFee</t>
+  </si>
+  <si>
+    <t>Oct 2025 - FFee</t>
+  </si>
+  <si>
+    <t>Nov 2025 - FFee</t>
+  </si>
+  <si>
+    <t>Dec 2025 - FFee</t>
+  </si>
+  <si>
+    <t>2025 Total Forecast Expenses</t>
+  </si>
+  <si>
+    <t>Jan 2025 - FExpenses</t>
+  </si>
+  <si>
+    <t>Feb 2025 - FExpenses</t>
+  </si>
+  <si>
+    <t>March 2025 - FExpenses</t>
+  </si>
+  <si>
+    <t>April 2025 - FExpenses</t>
+  </si>
+  <si>
+    <t>May 2025 - FExpenses</t>
+  </si>
+  <si>
+    <t>June 2025 - FExpenses</t>
+  </si>
+  <si>
+    <t>July 2025 - FExpenses</t>
+  </si>
+  <si>
+    <t>Aug 2025 - FExpenses</t>
+  </si>
+  <si>
+    <t>Sep 2025 - FExpenses</t>
+  </si>
+  <si>
+    <t>Oct 2025 - FExpenses</t>
+  </si>
+  <si>
+    <t>Nov 2025 - FExpenses</t>
+  </si>
+  <si>
+    <t>Dec 2025 - FExpenses</t>
+  </si>
+  <si>
+    <t>Forecast Total 2025</t>
+  </si>
+  <si>
     <t>Jan 2025 - FTotal</t>
-  </si>
-  <si>
-    <t>Feb 2025 - FTotal</t>
-  </si>
-  <si>
-    <t>March 2025 - FTotal</t>
-  </si>
-  <si>
-    <t>April 2025 - FTotal</t>
-  </si>
-  <si>
-    <t>May 2025 - FTotal</t>
-  </si>
-  <si>
-    <t>June 2025 - FTotal</t>
-  </si>
-  <si>
-    <t>July 2025 - FTotal</t>
-  </si>
-  <si>
-    <t>Aug 2025 - FTotal</t>
-  </si>
-  <si>
-    <t>Sep 2025 - FTotal</t>
-  </si>
-  <si>
-    <t>Oct 2025 - FTotal</t>
-  </si>
-  <si>
-    <t>Nov 2025 - FTotal</t>
-  </si>
-  <si>
-    <t>Dec 2025 - FTotal</t>
-  </si>
-  <si>
-    <t>2025 Forecast total Fee</t>
-  </si>
-  <si>
-    <t>Pfizer requested PO</t>
-  </si>
-  <si>
-    <t>IBM PMA</t>
-  </si>
-  <si>
-    <t>PO Owner</t>
-  </si>
-  <si>
-    <t>PO #</t>
-  </si>
-  <si>
-    <t>Work Code</t>
-  </si>
-  <si>
-    <t>Project Name</t>
-  </si>
-  <si>
-    <t>Project Start Date</t>
-  </si>
-  <si>
-    <t>Project End Date</t>
-  </si>
-  <si>
-    <t>Resource Talent Id</t>
-  </si>
-  <si>
-    <t>Resource Name</t>
-  </si>
-  <si>
-    <t>Bill Rate</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Resource Status</t>
-  </si>
-  <si>
-    <t>Forecast Month Hours</t>
-  </si>
-  <si>
-    <t>Actual Month Hours</t>
-  </si>
-  <si>
-    <t>Acual Fee $</t>
-  </si>
-  <si>
-    <t>Actual Expenses $</t>
-  </si>
-  <si>
-    <t>Actual Total $</t>
-  </si>
-  <si>
-    <t>Monthly Hours Variance</t>
-  </si>
-  <si>
-    <t>Hours Billed Flag</t>
-  </si>
-  <si>
-    <t>Forecast Accuracy</t>
-  </si>
-  <si>
-    <t>Expense%</t>
-  </si>
-  <si>
-    <t>Jan 2025 - FFHours</t>
-  </si>
-  <si>
-    <t>Feb 2025 - FHours</t>
-  </si>
-  <si>
-    <t>March 2025 - FHours</t>
-  </si>
-  <si>
-    <t>April 2025 - FHours</t>
-  </si>
-  <si>
-    <t>May 2025 - FHours</t>
-  </si>
-  <si>
-    <t>June 2025 - FHours</t>
-  </si>
-  <si>
-    <t>July 2025 - FHours</t>
-  </si>
-  <si>
-    <t>Aug 2025 - FHours</t>
-  </si>
-  <si>
-    <t>Sep 2025 - FHours</t>
-  </si>
-  <si>
-    <t>Oct 2025 - FHours</t>
-  </si>
-  <si>
-    <t>Nov 2025 - FHours</t>
-  </si>
-  <si>
-    <t>Dec 2025 - FHours</t>
-  </si>
-  <si>
-    <t>Jan 2025 - FFee</t>
-  </si>
-  <si>
-    <t>Feb 2025 - FFee</t>
-  </si>
-  <si>
-    <t>March 2025 - FFee</t>
-  </si>
-  <si>
-    <t>April 2025 - FFee</t>
-  </si>
-  <si>
-    <t>May 2025 - FFee</t>
-  </si>
-  <si>
-    <t>June 2025 - FFee</t>
-  </si>
-  <si>
-    <t>July 2025 - FFee</t>
-  </si>
-  <si>
-    <t>Aug 2025 - FFee</t>
-  </si>
-  <si>
-    <t>Sep 2025 - FFee</t>
-  </si>
-  <si>
-    <t>Oct 2025 - FFee</t>
-  </si>
-  <si>
-    <t>Nov 2025 - FFee</t>
-  </si>
-  <si>
-    <t>Dec 2025 - FFee</t>
-  </si>
-  <si>
-    <t>2025 Total Forecast Expenses</t>
-  </si>
-  <si>
-    <t>Jan 2025 - FExpenses</t>
-  </si>
-  <si>
-    <t>Feb 2025 - FExpenses</t>
-  </si>
-  <si>
-    <t>March 2025 - FExpenses</t>
-  </si>
-  <si>
-    <t>April 2025 - FExpenses</t>
-  </si>
-  <si>
-    <t>May 2025 - FExpenses</t>
-  </si>
-  <si>
-    <t>June 2025 - FExpenses</t>
-  </si>
-  <si>
-    <t>July 2025 - FExpenses</t>
-  </si>
-  <si>
-    <t>Aug 2025 - FExpenses</t>
-  </si>
-  <si>
-    <t>Sep 2025 - FExpenses</t>
-  </si>
-  <si>
-    <t>Oct 2025 - FExpenses</t>
-  </si>
-  <si>
-    <t>Nov 2025 - FExpenses</t>
-  </si>
-  <si>
-    <t>Dec 2025 - FExpenses</t>
-  </si>
-  <si>
-    <t>Forecast Total 2025</t>
   </si>
   <si>
     <t>No</t>
@@ -2526,7 +2526,7 @@
       <c r="R11" s="101"/>
       <c r="S11" s="99">
         <f t="array" ref="S11">SUM(V15:V17)+SUM(_xlfn._xlws.FILTER(U15:U17,V15:V17=""))+SUM(_xlfn._xlws.FILTER(T15:T17,(U15:U17="")*(V15:V17="")))+SUMIFS(W15:W17,V15:V17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(S15:S17)</f>
-        <v>0</v>
+        <v>81595.28</v>
       </c>
       <c r="T11" s="100"/>
       <c r="U11" s="100"/>
@@ -2534,7 +2534,7 @@
       <c r="W11" s="101"/>
       <c r="X11" s="99">
         <f t="array" ref="X11">SUM(AA15:AA17)+SUM(_xlfn._xlws.FILTER(Z15:Z17,AA15:AA17=""))+SUM(_xlfn._xlws.FILTER(Y15:Y17,(Z15:Z17="")*(AA15:AA17="")))+SUMIFS(AB15:AB17,AA15:AA17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(X15:X17)</f>
-        <v>0</v>
+        <v>46818.44</v>
       </c>
       <c r="Y11" s="100"/>
       <c r="Z11" s="100"/>
@@ -2542,7 +2542,7 @@
       <c r="AB11" s="101"/>
       <c r="AC11" s="99">
         <f t="array" ref="AC11">SUM(AF15:AF17)+SUM(_xlfn._xlws.FILTER(AE15:AE17,AF15:AF17=""))+SUM(_xlfn._xlws.FILTER(AD15:AD17,(AE15:AE17="")*(AF15:AF17="")))+SUMIFS(AG15:AG17,AF15:AF17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(AC15:AC17)</f>
-        <v>0</v>
+        <v>-15519.220000000001</v>
       </c>
       <c r="AD11" s="100"/>
       <c r="AE11" s="100"/>
@@ -2550,7 +2550,7 @@
       <c r="AG11" s="101"/>
       <c r="AH11" s="99">
         <f t="array" ref="AH11">SUM(AK15:AK17)+SUM(_xlfn._xlws.FILTER(AJ15:AJ17,AK15:AK17=""))+SUM(_xlfn._xlws.FILTER(AI15:AI17,(AJ15:AJ17="")*(AK15:AK17="")))+SUMIFS(AL15:AL17,AK15:AK17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(AH15:AH17)</f>
-        <v>0</v>
+        <v>29658.28</v>
       </c>
       <c r="AI11" s="100"/>
       <c r="AJ11" s="100"/>
@@ -2558,7 +2558,7 @@
       <c r="AL11" s="101"/>
       <c r="AM11" s="99">
         <f t="array" ref="AM11">SUM(AP15:AP17)+SUM(_xlfn._xlws.FILTER(AO15:AO17,AP15:AP17=""))+SUM(_xlfn._xlws.FILTER(AN15:AN17,(AO15:AO17="")*(AP15:AP17="")))+SUMIFS(AQ15:AQ17,AP15:AP17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(AM15:AM17)</f>
-        <v>0</v>
+        <v>-13038.279999999999</v>
       </c>
       <c r="AN11" s="100"/>
       <c r="AO11" s="100"/>
@@ -2566,7 +2566,7 @@
       <c r="AQ11" s="101"/>
       <c r="AR11" s="99">
         <f t="array" ref="AR11">SUM(AU15:AU17)+SUM(_xlfn._xlws.FILTER(AT15:AT17,AU15:AU17=""))+SUM(_xlfn._xlws.FILTER(AS15:AS17,(AT15:AT17="")*(AU15:AU17="")))+SUMIFS(AV15:AV17,AU15:AU17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(AR15:AR17)</f>
-        <v>0</v>
+        <v>-55230.5</v>
       </c>
       <c r="AS11" s="100"/>
       <c r="AT11" s="100"/>
@@ -2574,7 +2574,7 @@
       <c r="AV11" s="101"/>
       <c r="AW11" s="99">
         <f t="array" ref="AW11">SUM(AZ15:AZ17)+SUM(_xlfn._xlws.FILTER(AY15:AY17,AZ15:AZ17=""))+SUM(_xlfn._xlws.FILTER(AX15:AX17,(AY15:AY17="")*(AZ15:AZ17="")))+SUMIFS(BA15:BA17,AZ15:AZ17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(AW15:AW17)</f>
-        <v>0</v>
+        <v>-60651.5</v>
       </c>
       <c r="AX11" s="100"/>
       <c r="AY11" s="100"/>
@@ -2582,7 +2582,7 @@
       <c r="BA11" s="101"/>
       <c r="BB11" s="99">
         <f t="array" ref="BB11">SUM(BE15:BE17)+SUM(_xlfn._xlws.FILTER(BD15:BD17,BE15:BE17=""))+SUM(_xlfn._xlws.FILTER(BC15:BC17,(BD15:BD17="")*(BE15:BE17="")))+SUMIFS(BF15:BF17,BE15:BE17,"&lt;&gt;"&amp;"",$P$15:$P$17,"&lt;&gt;"&amp;"")+SUM(BB15:BB17)</f>
-        <v>0</v>
+        <v>57824</v>
       </c>
       <c r="BC11" s="100"/>
       <c r="BD11" s="100"/>
@@ -2643,7 +2643,7 @@
       <c r="M12" s="106"/>
       <c r="N12" s="99">
         <f t="array" ref="N12">SUM(Q15:Q17)+SUM(_xlfn._xlws.FILTER(P15:P17,Q15:Q17=""))+SUM(_xlfn._xlws.FILTER(O15:O17,(P15:P17="")*(Q15:Q17="")))</f>
-        <v>0</v>
+        <v>47862.5</v>
       </c>
       <c r="O12" s="100"/>
       <c r="P12" s="100"/>
@@ -2651,7 +2651,7 @@
       <c r="R12" s="101"/>
       <c r="S12" s="99">
         <f t="array" ref="S12">SUM(V15:V17)+SUM(_xlfn._xlws.FILTER(U15:U17,V15:V17=""))+SUM(_xlfn._xlws.FILTER(T15:T17,(U15:U17="")*(V15:V17="")))</f>
-        <v>0</v>
+        <v>17100</v>
       </c>
       <c r="T12" s="100"/>
       <c r="U12" s="100"/>
@@ -2659,7 +2659,7 @@
       <c r="W12" s="101"/>
       <c r="X12" s="99">
         <f t="array" ref="X12">SUM(AA15:AA17)+SUM(_xlfn._xlws.FILTER(Z15:Z17,AA15:AA17=""))+SUM(_xlfn._xlws.FILTER(Y15:Y17,(Z15:Z17="")*(AA15:AA17="")))</f>
-        <v>0</v>
+        <v>79073</v>
       </c>
       <c r="Y12" s="100"/>
       <c r="Z12" s="100"/>
@@ -2667,7 +2667,7 @@
       <c r="AB12" s="101"/>
       <c r="AC12" s="99">
         <f t="array" ref="AC12">SUM(AF15:AF17)+SUM(_xlfn._xlws.FILTER(AE15:AE17,AF15:AF17=""))+SUM(_xlfn._xlws.FILTER(AD15:AD17,(AE15:AE17="")*(AF15:AF17="")))</f>
-        <v>0</v>
+        <v>36207.5</v>
       </c>
       <c r="AD12" s="100"/>
       <c r="AE12" s="100"/>
@@ -2675,7 +2675,7 @@
       <c r="AG12" s="101"/>
       <c r="AH12" s="99">
         <f t="array" ref="AH12">SUM(AK15:AK17)+SUM(_xlfn._xlws.FILTER(AJ15:AJ17,AK15:AK17=""))+SUM(_xlfn._xlws.FILTER(AI15:AI17,(AJ15:AJ17="")*(AK15:AK17="")))</f>
-        <v>0</v>
+        <v>113922.5</v>
       </c>
       <c r="AI12" s="100"/>
       <c r="AJ12" s="100"/>
@@ -2683,7 +2683,7 @@
       <c r="AL12" s="101"/>
       <c r="AM12" s="99">
         <f t="array" ref="AM12">SUM(AP15:AP17)+SUM(_xlfn._xlws.FILTER(AO15:AO17,AP15:AP17=""))+SUM(_xlfn._xlws.FILTER(AN15:AN17,(AO15:AO17="")*(AP15:AP17="")))</f>
-        <v>0</v>
+        <v>55230.5</v>
       </c>
       <c r="AN12" s="100"/>
       <c r="AO12" s="100"/>
@@ -2691,7 +2691,7 @@
       <c r="AQ12" s="101"/>
       <c r="AR12" s="99">
         <f t="array" ref="AR12">SUM(AU15:AU17)+SUM(_xlfn._xlws.FILTER(AT15:AT17,AU15:AU17=""))+SUM(_xlfn._xlws.FILTER(AS15:AS17,(AT15:AT17="")*(AU15:AU17="")))</f>
-        <v>0</v>
+        <v>427.5</v>
       </c>
       <c r="AS12" s="100"/>
       <c r="AT12" s="100"/>
@@ -2699,7 +2699,7 @@
       <c r="AV12" s="101"/>
       <c r="AW12" s="99">
         <f t="array" ref="AW12">SUM(AZ15:AZ17)+SUM(_xlfn._xlws.FILTER(AY15:AY17,AZ15:AZ17=""))+SUM(_xlfn._xlws.FILTER(AX15:AX17,(AY15:AY17="")*(AZ15:AZ17="")))</f>
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="AX12" s="100"/>
       <c r="AY12" s="100"/>
@@ -3102,11 +3102,11 @@
         <v>0</v>
       </c>
       <c r="Q15" s="87">
-        <v>0</v>
+        <v>13822.5</v>
       </c>
       <c r="R15" s="87">
         <f>P15-Q15</f>
-        <v>0</v>
+        <v>-13822.5</v>
       </c>
       <c r="S15" s="88">
         <v>0</v>
@@ -3115,126 +3115,126 @@
         <v>10212.5</v>
       </c>
       <c r="U15" s="86">
-        <v>0</v>
+        <v>19385.28</v>
       </c>
       <c r="V15" s="87">
-        <v>0</v>
+        <v>17100</v>
       </c>
       <c r="W15" s="89">
         <f>U15-V15</f>
-        <v>0</v>
+        <v>2285.2799999999988</v>
       </c>
       <c r="X15" s="90">
-        <v>0</v>
+        <v>-19385.28</v>
       </c>
       <c r="Y15" s="86">
         <v>21375</v>
       </c>
       <c r="Z15" s="86">
-        <v>0</v>
+        <v>22813.72</v>
       </c>
       <c r="AA15" s="87">
-        <v>0</v>
+        <v>20425</v>
       </c>
       <c r="AB15" s="89">
         <f>Z15-AA15</f>
-        <v>0</v>
+        <v>2388.7200000000012</v>
       </c>
       <c r="AC15" s="90">
-        <v>0</v>
+        <v>-22813.72</v>
       </c>
       <c r="AD15" s="86">
         <v>15390</v>
       </c>
       <c r="AE15" s="86">
-        <v>0</v>
+        <v>19294.5</v>
       </c>
       <c r="AF15" s="86">
-        <v>0</v>
+        <v>15247.5</v>
       </c>
       <c r="AG15" s="89">
         <f>AE15-AF15</f>
-        <v>0</v>
+        <v>4047</v>
       </c>
       <c r="AH15" s="90">
-        <v>0</v>
+        <v>-19294.5</v>
       </c>
       <c r="AI15" s="86">
         <v>17100</v>
       </c>
       <c r="AJ15" s="86">
-        <v>0</v>
+        <v>20952.78</v>
       </c>
       <c r="AK15" s="86">
-        <v>0</v>
+        <v>11162.5</v>
       </c>
       <c r="AL15" s="89">
         <f>AJ15-AK15</f>
-        <v>0</v>
+        <v>9790.2799999999988</v>
       </c>
       <c r="AM15" s="90">
-        <v>0</v>
+        <v>-20952.78</v>
       </c>
       <c r="AN15" s="86">
         <v>21375</v>
       </c>
       <c r="AO15" s="86">
-        <v>0</v>
+        <v>30922.5</v>
       </c>
       <c r="AP15" s="86">
-        <v>0</v>
+        <v>16862.5</v>
       </c>
       <c r="AQ15" s="89">
         <f>AO15-AP15</f>
-        <v>0</v>
+        <v>14060</v>
       </c>
       <c r="AR15" s="90">
-        <v>0</v>
+        <v>-30922.5</v>
       </c>
       <c r="AS15" s="86">
         <v>855</v>
       </c>
       <c r="AT15" s="86">
-        <v>0</v>
+        <v>14060</v>
       </c>
       <c r="AU15" s="86">
-        <v>0</v>
+        <v>427.5</v>
       </c>
       <c r="AV15" s="89">
         <f>AT15-AU15</f>
-        <v>0</v>
+        <v>13632.5</v>
       </c>
       <c r="AW15" s="90">
-        <v>0</v>
+        <v>-14060</v>
       </c>
       <c r="AX15" s="86">
         <v>0</v>
       </c>
       <c r="AY15" s="86">
-        <v>0</v>
+        <v>13632.5</v>
       </c>
       <c r="AZ15" s="86">
         <v>0</v>
       </c>
       <c r="BA15" s="89">
         <f>AY15-AZ15</f>
-        <v>0</v>
+        <v>13632.5</v>
       </c>
       <c r="BB15" s="90">
-        <v>0</v>
+        <v>-13632.5</v>
       </c>
       <c r="BC15" s="86">
         <v>0</v>
       </c>
       <c r="BD15" s="86">
-        <v>0</v>
+        <v>13632.5</v>
       </c>
       <c r="BE15" s="86">
         <v>0</v>
       </c>
       <c r="BF15" s="89">
         <f>BD15-BE15</f>
-        <v>0</v>
+        <v>13632.5</v>
       </c>
       <c r="BG15" s="90">
         <v>0</v>
@@ -3379,11 +3379,11 @@
         <v>0</v>
       </c>
       <c r="Q16" s="87">
-        <v>0</v>
+        <v>34040</v>
       </c>
       <c r="R16" s="87">
         <f>P16-Q16</f>
-        <v>0</v>
+        <v>-34040</v>
       </c>
       <c r="S16" s="88">
         <v>0</v>
@@ -3392,97 +3392,97 @@
         <v>30420</v>
       </c>
       <c r="U16" s="86">
-        <v>0</v>
+        <v>62210</v>
       </c>
       <c r="V16" s="87">
         <v>0</v>
       </c>
       <c r="W16" s="89">
         <f>U16-V16</f>
-        <v>0</v>
+        <v>62210</v>
       </c>
       <c r="X16" s="90">
-        <v>0</v>
+        <v>-78320</v>
       </c>
       <c r="Y16" s="86">
         <v>60000</v>
       </c>
       <c r="Z16" s="86">
-        <v>0</v>
+        <v>121710</v>
       </c>
       <c r="AA16" s="87">
-        <v>0</v>
+        <v>58648</v>
       </c>
       <c r="AB16" s="89">
         <f>Z16-AA16</f>
-        <v>0</v>
+        <v>63062</v>
       </c>
       <c r="AC16" s="90">
-        <v>0</v>
+        <v>-140172</v>
       </c>
       <c r="AD16" s="86">
         <v>48000</v>
       </c>
       <c r="AE16" s="86">
-        <v>0</v>
+        <v>128172</v>
       </c>
       <c r="AF16" s="87">
-        <v>0</v>
+        <v>20960</v>
       </c>
       <c r="AG16" s="89">
         <f>AE16-AF16</f>
-        <v>0</v>
+        <v>107212</v>
       </c>
       <c r="AH16" s="90">
-        <v>0</v>
+        <v>-130564</v>
       </c>
       <c r="AI16" s="86">
         <v>48000</v>
       </c>
       <c r="AJ16" s="86">
-        <v>0</v>
+        <v>158564</v>
       </c>
       <c r="AK16" s="87">
-        <v>0</v>
+        <v>102760</v>
       </c>
       <c r="AL16" s="89">
         <f>AJ16-AK16</f>
-        <v>0</v>
+        <v>55804</v>
       </c>
       <c r="AM16" s="90">
-        <v>0</v>
+        <v>-140102</v>
       </c>
       <c r="AN16" s="86">
         <v>57600</v>
       </c>
       <c r="AO16" s="86">
-        <v>0</v>
+        <v>117094</v>
       </c>
       <c r="AP16" s="87">
-        <v>0</v>
+        <v>38368</v>
       </c>
       <c r="AQ16" s="89">
         <f>AO16-AP16</f>
-        <v>0</v>
+        <v>78726</v>
       </c>
       <c r="AR16" s="90">
-        <v>0</v>
+        <v>-98592</v>
       </c>
       <c r="AS16" s="86">
         <v>2400</v>
       </c>
       <c r="AT16" s="86">
-        <v>0</v>
+        <v>60224</v>
       </c>
       <c r="AU16" s="87">
         <v>0</v>
       </c>
       <c r="AV16" s="89">
         <f>AT16-AU16</f>
-        <v>0</v>
+        <v>60224</v>
       </c>
       <c r="AW16" s="90">
-        <v>0</v>
+        <v>-60224</v>
       </c>
       <c r="AX16" s="86">
         <v>0</v>
@@ -3491,11 +3491,11 @@
         <v>0</v>
       </c>
       <c r="AZ16" s="87">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="BA16" s="89">
         <f>AY16-AZ16</f>
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="BB16" s="90">
         <v>0</v>
@@ -3504,14 +3504,14 @@
         <v>0</v>
       </c>
       <c r="BD16" s="86">
-        <v>0</v>
+        <v>57824</v>
       </c>
       <c r="BE16" s="87">
         <v>0</v>
       </c>
       <c r="BF16" s="89">
         <f>BD16-BE16</f>
-        <v>0</v>
+        <v>57824</v>
       </c>
       <c r="BG16" s="90">
         <v>0</v>
@@ -3815,21 +3815,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:CA6"/>
+  <dimension ref="A1:BZ6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="6" width="19" customWidth="1"/>
-    <col min="7" max="8" width="21" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="11" width="20" customWidth="1"/>
-    <col min="12" max="16" width="19" customWidth="1"/>
-    <col min="17" max="17" width="25" customWidth="1"/>
-    <col min="18" max="78" width="21" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="79" max="79" width="9.140625" collapsed="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="4" width="21" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="7" width="20" customWidth="1"/>
+    <col min="8" max="12" width="19" customWidth="1"/>
+    <col min="13" max="78" width="21" customWidth="1" outlineLevel="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:78" x14ac:dyDescent="0.25">
@@ -3942,16 +3937,16 @@
         <v>123</v>
       </c>
       <c r="AK1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL1" t="s">
         <v>124</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>125</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>126</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>83</v>
       </c>
       <c r="AO1" t="s">
         <v>127</v>
@@ -4069,609 +4064,609 @@
       </c>
     </row>
     <row r="2" spans="1:78" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>0</v>
+      <c r="A2" t="s">
+        <v>84</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>4275</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>10687.5</v>
       </c>
       <c r="D2">
+        <v>7695</v>
+      </c>
+      <c r="E2">
+        <v>8550</v>
+      </c>
+      <c r="F2">
+        <v>10687.5</v>
+      </c>
+      <c r="G2">
+        <v>427.5</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N2" t="s">
+        <v>166</v>
+      </c>
+      <c r="O2" t="s">
+        <v>167</v>
+      </c>
+      <c r="P2" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>169</v>
+      </c>
+      <c r="R2" s="98">
+        <v>45658</v>
+      </c>
+      <c r="S2" s="98">
+        <v>45838</v>
+      </c>
+      <c r="T2" t="s">
+        <v>170</v>
+      </c>
+      <c r="U2" t="s">
+        <v>171</v>
+      </c>
+      <c r="V2">
+        <v>47.5</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>1</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
         <v>1048</v>
       </c>
-      <c r="E2">
+      <c r="AM2">
+        <v>157</v>
+      </c>
+      <c r="AN2">
+        <v>90</v>
+      </c>
+      <c r="AO2">
+        <v>225</v>
+      </c>
+      <c r="AP2">
+        <v>162</v>
+      </c>
+      <c r="AQ2">
+        <v>180</v>
+      </c>
+      <c r="AR2">
+        <v>225</v>
+      </c>
+      <c r="AS2">
+        <v>9</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>49780</v>
+      </c>
+      <c r="AZ2">
         <v>7457.5</v>
       </c>
-      <c r="F2">
+      <c r="BA2">
         <v>4275</v>
       </c>
-      <c r="G2">
+      <c r="BB2">
         <v>10687.5</v>
       </c>
-      <c r="H2">
+      <c r="BC2">
         <v>7695</v>
       </c>
-      <c r="I2">
+      <c r="BD2">
         <v>8550</v>
       </c>
-      <c r="J2">
+      <c r="BE2">
         <v>10687.5</v>
       </c>
-      <c r="K2">
+      <c r="BF2">
         <v>427.5</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
+      <c r="BG2">
+        <v>0</v>
+      </c>
+      <c r="BH2">
+        <v>0</v>
+      </c>
+      <c r="BI2">
+        <v>0</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BM2">
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <v>0</v>
+      </c>
+      <c r="BO2">
+        <v>0</v>
+      </c>
+      <c r="BP2">
+        <v>0</v>
+      </c>
+      <c r="BQ2">
+        <v>0</v>
+      </c>
+      <c r="BR2">
+        <v>0</v>
+      </c>
+      <c r="BS2">
+        <v>0</v>
+      </c>
+      <c r="BT2">
+        <v>0</v>
+      </c>
+      <c r="BU2">
+        <v>0</v>
+      </c>
+      <c r="BV2">
+        <v>0</v>
+      </c>
+      <c r="BW2">
+        <v>0</v>
+      </c>
+      <c r="BX2">
+        <v>0</v>
+      </c>
+      <c r="BY2">
         <v>49780</v>
       </c>
-      <c r="R2" t="s">
-        <v>165</v>
-      </c>
-      <c r="S2" t="s">
-        <v>166</v>
-      </c>
-      <c r="T2" t="s">
-        <v>167</v>
-      </c>
-      <c r="U2">
-        <v>9500879389</v>
-      </c>
-      <c r="V2" t="s">
-        <v>168</v>
-      </c>
-      <c r="W2" t="s">
-        <v>169</v>
-      </c>
-      <c r="X2" s="98">
-        <v>45658</v>
-      </c>
-      <c r="Y2" s="98">
-        <v>45838</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>170</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>171</v>
-      </c>
-      <c r="AB2">
-        <v>47.5</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>1</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>157</v>
-      </c>
-      <c r="AP2">
-        <v>90</v>
-      </c>
-      <c r="AQ2">
-        <v>225</v>
-      </c>
-      <c r="AR2">
-        <v>162</v>
-      </c>
-      <c r="AS2">
-        <v>180</v>
-      </c>
-      <c r="AT2">
-        <v>225</v>
-      </c>
-      <c r="AU2">
-        <v>9</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
+      <c r="BZ2">
         <v>7457.5</v>
-      </c>
-      <c r="BB2">
-        <v>4275</v>
-      </c>
-      <c r="BC2">
-        <v>10687.5</v>
-      </c>
-      <c r="BD2">
-        <v>7695</v>
-      </c>
-      <c r="BE2">
-        <v>8550</v>
-      </c>
-      <c r="BF2">
-        <v>10687.5</v>
-      </c>
-      <c r="BG2">
-        <v>427.5</v>
-      </c>
-      <c r="BH2">
-        <v>0</v>
-      </c>
-      <c r="BI2">
-        <v>0</v>
-      </c>
-      <c r="BJ2">
-        <v>0</v>
-      </c>
-      <c r="BK2">
-        <v>0</v>
-      </c>
-      <c r="BL2">
-        <v>0</v>
-      </c>
-      <c r="BM2">
-        <v>0</v>
-      </c>
-      <c r="BN2">
-        <v>0</v>
-      </c>
-      <c r="BO2">
-        <v>0</v>
-      </c>
-      <c r="BP2">
-        <v>0</v>
-      </c>
-      <c r="BQ2">
-        <v>0</v>
-      </c>
-      <c r="BR2">
-        <v>0</v>
-      </c>
-      <c r="BS2">
-        <v>0</v>
-      </c>
-      <c r="BT2">
-        <v>0</v>
-      </c>
-      <c r="BU2">
-        <v>0</v>
-      </c>
-      <c r="BV2">
-        <v>0</v>
-      </c>
-      <c r="BW2">
-        <v>0</v>
-      </c>
-      <c r="BX2">
-        <v>0</v>
-      </c>
-      <c r="BY2">
-        <v>0</v>
-      </c>
-      <c r="BZ2">
-        <v>49780</v>
       </c>
     </row>
     <row r="3" spans="1:78" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>0</v>
+      <c r="A3" t="s">
+        <v>84</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>5937.5</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>10687.5</v>
       </c>
       <c r="D3">
+        <v>7695</v>
+      </c>
+      <c r="E3">
+        <v>8550</v>
+      </c>
+      <c r="F3">
+        <v>10687.5</v>
+      </c>
+      <c r="G3">
+        <v>427.5</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" t="s">
+        <v>165</v>
+      </c>
+      <c r="N3" t="s">
+        <v>166</v>
+      </c>
+      <c r="O3" t="s">
+        <v>167</v>
+      </c>
+      <c r="P3" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>169</v>
+      </c>
+      <c r="R3" s="98">
+        <v>45658</v>
+      </c>
+      <c r="S3" s="98">
+        <v>45838</v>
+      </c>
+      <c r="T3" t="s">
+        <v>172</v>
+      </c>
+      <c r="U3" t="s">
+        <v>173</v>
+      </c>
+      <c r="V3">
+        <v>47.5</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>1</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
         <v>1074</v>
       </c>
-      <c r="E3">
+      <c r="AM3">
+        <v>148</v>
+      </c>
+      <c r="AN3">
+        <v>125</v>
+      </c>
+      <c r="AO3">
+        <v>225</v>
+      </c>
+      <c r="AP3">
+        <v>162</v>
+      </c>
+      <c r="AQ3">
+        <v>180</v>
+      </c>
+      <c r="AR3">
+        <v>225</v>
+      </c>
+      <c r="AS3">
+        <v>9</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>51015</v>
+      </c>
+      <c r="AZ3">
         <v>7030</v>
       </c>
-      <c r="F3">
+      <c r="BA3">
         <v>5937.5</v>
       </c>
-      <c r="G3">
+      <c r="BB3">
         <v>10687.5</v>
       </c>
-      <c r="H3">
+      <c r="BC3">
         <v>7695</v>
       </c>
-      <c r="I3">
+      <c r="BD3">
         <v>8550</v>
       </c>
-      <c r="J3">
+      <c r="BE3">
         <v>10687.5</v>
       </c>
-      <c r="K3">
+      <c r="BF3">
         <v>427.5</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3">
         <v>51015</v>
       </c>
-      <c r="R3" t="s">
-        <v>165</v>
-      </c>
-      <c r="S3" t="s">
-        <v>166</v>
-      </c>
-      <c r="T3" t="s">
-        <v>167</v>
-      </c>
-      <c r="U3">
-        <v>9500879389</v>
-      </c>
-      <c r="V3" t="s">
-        <v>168</v>
-      </c>
-      <c r="W3" t="s">
-        <v>169</v>
-      </c>
-      <c r="X3" s="98">
-        <v>45658</v>
-      </c>
-      <c r="Y3" s="98">
-        <v>45838</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>173</v>
-      </c>
-      <c r="AB3">
-        <v>47.5</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>1</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>148</v>
-      </c>
-      <c r="AP3">
-        <v>125</v>
-      </c>
-      <c r="AQ3">
-        <v>225</v>
-      </c>
-      <c r="AR3">
-        <v>162</v>
-      </c>
-      <c r="AS3">
-        <v>180</v>
-      </c>
-      <c r="AT3">
-        <v>225</v>
-      </c>
-      <c r="AU3">
-        <v>9</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
+      <c r="BZ3">
         <v>7030</v>
-      </c>
-      <c r="BB3">
-        <v>5937.5</v>
-      </c>
-      <c r="BC3">
-        <v>10687.5</v>
-      </c>
-      <c r="BD3">
-        <v>7695</v>
-      </c>
-      <c r="BE3">
-        <v>8550</v>
-      </c>
-      <c r="BF3">
-        <v>10687.5</v>
-      </c>
-      <c r="BG3">
-        <v>427.5</v>
-      </c>
-      <c r="BH3">
-        <v>0</v>
-      </c>
-      <c r="BI3">
-        <v>0</v>
-      </c>
-      <c r="BJ3">
-        <v>0</v>
-      </c>
-      <c r="BK3">
-        <v>0</v>
-      </c>
-      <c r="BL3">
-        <v>0</v>
-      </c>
-      <c r="BM3">
-        <v>0</v>
-      </c>
-      <c r="BN3">
-        <v>0</v>
-      </c>
-      <c r="BO3">
-        <v>0</v>
-      </c>
-      <c r="BP3">
-        <v>0</v>
-      </c>
-      <c r="BQ3">
-        <v>0</v>
-      </c>
-      <c r="BR3">
-        <v>0</v>
-      </c>
-      <c r="BS3">
-        <v>0</v>
-      </c>
-      <c r="BT3">
-        <v>0</v>
-      </c>
-      <c r="BU3">
-        <v>0</v>
-      </c>
-      <c r="BV3">
-        <v>0</v>
-      </c>
-      <c r="BW3">
-        <v>0</v>
-      </c>
-      <c r="BX3">
-        <v>0</v>
-      </c>
-      <c r="BY3">
-        <v>0</v>
-      </c>
-      <c r="BZ3">
-        <v>51015</v>
       </c>
     </row>
     <row r="4" spans="1:78" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>0</v>
+      <c r="A4" t="s">
+        <v>85</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>26200</v>
       </c>
       <c r="D4">
+        <v>20960</v>
+      </c>
+      <c r="E4">
+        <v>20960</v>
+      </c>
+      <c r="F4">
+        <v>25152</v>
+      </c>
+      <c r="G4">
+        <v>1048</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" t="s">
+        <v>174</v>
+      </c>
+      <c r="N4" t="s">
+        <v>166</v>
+      </c>
+      <c r="O4" t="s">
+        <v>167</v>
+      </c>
+      <c r="P4" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>169</v>
+      </c>
+      <c r="R4" s="98">
+        <v>45658</v>
+      </c>
+      <c r="S4" s="98">
+        <v>45838</v>
+      </c>
+      <c r="T4" t="s">
+        <v>175</v>
+      </c>
+      <c r="U4" t="s">
+        <v>176</v>
+      </c>
+      <c r="V4">
+        <v>131</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>1</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
         <v>720</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>200</v>
+      </c>
+      <c r="AP4">
+        <v>160</v>
+      </c>
+      <c r="AQ4">
+        <v>160</v>
+      </c>
+      <c r="AR4">
+        <v>192</v>
+      </c>
+      <c r="AS4">
+        <v>8</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>94320</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
         <v>26200</v>
       </c>
-      <c r="H4">
+      <c r="BC4">
         <v>20960</v>
-      </c>
-      <c r="I4">
-        <v>20960</v>
-      </c>
-      <c r="J4">
-        <v>25152</v>
-      </c>
-      <c r="K4">
-        <v>1048</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>94320</v>
-      </c>
-      <c r="R4" t="s">
-        <v>174</v>
-      </c>
-      <c r="S4" t="s">
-        <v>166</v>
-      </c>
-      <c r="T4" t="s">
-        <v>167</v>
-      </c>
-      <c r="U4">
-        <v>9500882917</v>
-      </c>
-      <c r="V4" t="s">
-        <v>168</v>
-      </c>
-      <c r="W4" t="s">
-        <v>169</v>
-      </c>
-      <c r="X4" s="98">
-        <v>45658</v>
-      </c>
-      <c r="Y4" s="98">
-        <v>45838</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB4">
-        <v>131</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>1</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>200</v>
-      </c>
-      <c r="AR4">
-        <v>160</v>
-      </c>
-      <c r="AS4">
-        <v>160</v>
-      </c>
-      <c r="AT4">
-        <v>192</v>
-      </c>
-      <c r="AU4">
-        <v>8</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>0</v>
-      </c>
-      <c r="BC4">
-        <v>26200</v>
       </c>
       <c r="BD4">
         <v>20960</v>
       </c>
       <c r="BE4">
-        <v>20960</v>
+        <v>25152</v>
       </c>
       <c r="BF4">
-        <v>25152</v>
+        <v>1048</v>
       </c>
       <c r="BG4">
-        <v>1048</v>
+        <v>0</v>
       </c>
       <c r="BH4">
         <v>0</v>
@@ -4725,174 +4720,174 @@
         <v>0</v>
       </c>
       <c r="BY4">
-        <v>0</v>
+        <v>94320</v>
       </c>
       <c r="BZ4">
-        <v>94320</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:78" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>0</v>
+      <c r="A5" t="s">
+        <v>85</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>30420</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>33800</v>
       </c>
       <c r="D5">
+        <v>27040</v>
+      </c>
+      <c r="E5">
+        <v>27040</v>
+      </c>
+      <c r="F5">
+        <v>32448</v>
+      </c>
+      <c r="G5">
+        <v>1352</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>174</v>
+      </c>
+      <c r="N5" t="s">
+        <v>166</v>
+      </c>
+      <c r="O5" t="s">
+        <v>167</v>
+      </c>
+      <c r="P5" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>169</v>
+      </c>
+      <c r="R5" s="98">
+        <v>45658</v>
+      </c>
+      <c r="S5" s="98">
+        <v>45838</v>
+      </c>
+      <c r="T5" t="s">
+        <v>177</v>
+      </c>
+      <c r="U5" t="s">
+        <v>178</v>
+      </c>
+      <c r="V5">
+        <v>169</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
         <v>1053</v>
       </c>
-      <c r="E5">
+      <c r="AM5">
+        <v>153</v>
+      </c>
+      <c r="AN5">
+        <v>180</v>
+      </c>
+      <c r="AO5">
+        <v>200</v>
+      </c>
+      <c r="AP5">
+        <v>160</v>
+      </c>
+      <c r="AQ5">
+        <v>160</v>
+      </c>
+      <c r="AR5">
+        <v>192</v>
+      </c>
+      <c r="AS5">
+        <v>8</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>177957</v>
+      </c>
+      <c r="AZ5">
         <v>25857</v>
       </c>
-      <c r="F5">
+      <c r="BA5">
         <v>30420</v>
       </c>
-      <c r="G5">
+      <c r="BB5">
         <v>33800</v>
       </c>
-      <c r="H5">
+      <c r="BC5">
         <v>27040</v>
-      </c>
-      <c r="I5">
-        <v>27040</v>
-      </c>
-      <c r="J5">
-        <v>32448</v>
-      </c>
-      <c r="K5">
-        <v>1352</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>177957</v>
-      </c>
-      <c r="R5" t="s">
-        <v>174</v>
-      </c>
-      <c r="S5" t="s">
-        <v>166</v>
-      </c>
-      <c r="T5" t="s">
-        <v>167</v>
-      </c>
-      <c r="U5">
-        <v>9500882917</v>
-      </c>
-      <c r="V5" t="s">
-        <v>168</v>
-      </c>
-      <c r="W5" t="s">
-        <v>169</v>
-      </c>
-      <c r="X5" s="98">
-        <v>45658</v>
-      </c>
-      <c r="Y5" s="98">
-        <v>45838</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>177</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB5">
-        <v>169</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <v>1</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>153</v>
-      </c>
-      <c r="AP5">
-        <v>180</v>
-      </c>
-      <c r="AQ5">
-        <v>200</v>
-      </c>
-      <c r="AR5">
-        <v>160</v>
-      </c>
-      <c r="AS5">
-        <v>160</v>
-      </c>
-      <c r="AT5">
-        <v>192</v>
-      </c>
-      <c r="AU5">
-        <v>8</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>25857</v>
-      </c>
-      <c r="BB5">
-        <v>30420</v>
-      </c>
-      <c r="BC5">
-        <v>33800</v>
       </c>
       <c r="BD5">
         <v>27040</v>
       </c>
       <c r="BE5">
-        <v>27040</v>
+        <v>32448</v>
       </c>
       <c r="BF5">
-        <v>32448</v>
+        <v>1352</v>
       </c>
       <c r="BG5">
-        <v>1352</v>
+        <v>0</v>
       </c>
       <c r="BH5">
         <v>0</v>
@@ -4946,259 +4941,59 @@
         <v>0</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>177957</v>
       </c>
       <c r="BZ5">
-        <v>177957</v>
+        <v>25857</v>
       </c>
     </row>
     <row r="6" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>179</v>
       </c>
-      <c r="R6">
-        <f t="shared" ref="R6:AW6" si="0">SUBTOTAL(9, R2:R5)</f>
-        <v>0</v>
-      </c>
-      <c r="S6">
+      <c r="B6">
+        <f t="shared" ref="B6:L6" si="0">SUBTOTAL(9,B2:B5)</f>
+        <v>40632.5</v>
+      </c>
+      <c r="C6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T6">
+        <v>81375</v>
+      </c>
+      <c r="D6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U6">
+        <v>63390</v>
+      </c>
+      <c r="E6">
         <f t="shared" si="0"/>
-        <v>38003524612</v>
-      </c>
-      <c r="V6">
+        <v>65100</v>
+      </c>
+      <c r="F6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W6">
+        <v>78975</v>
+      </c>
+      <c r="G6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X6">
+        <v>3255</v>
+      </c>
+      <c r="H6">
         <f t="shared" si="0"/>
-        <v>182632</v>
-      </c>
-      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <f t="shared" si="0"/>
-        <v>183352</v>
-      </c>
-      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA6">
+      <c r="K6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB6">
+      <c r="L6">
         <f t="shared" si="0"/>
-        <v>395</v>
-      </c>
-      <c r="AC6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AH6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AM6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <f t="shared" si="0"/>
-        <v>458</v>
-      </c>
-      <c r="AP6">
-        <f t="shared" si="0"/>
-        <v>395</v>
-      </c>
-      <c r="AQ6">
-        <f t="shared" si="0"/>
-        <v>850</v>
-      </c>
-      <c r="AR6">
-        <f t="shared" si="0"/>
-        <v>644</v>
-      </c>
-      <c r="AS6">
-        <f t="shared" si="0"/>
-        <v>680</v>
-      </c>
-      <c r="AT6">
-        <f t="shared" si="0"/>
-        <v>834</v>
-      </c>
-      <c r="AU6">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="AV6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <f t="shared" ref="AX6:CC6" si="1">SUBTOTAL(9, AX2:AX5)</f>
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <f t="shared" si="1"/>
-        <v>40344.5</v>
-      </c>
-      <c r="BB6">
-        <f t="shared" si="1"/>
-        <v>40632.5</v>
-      </c>
-      <c r="BC6">
-        <f t="shared" si="1"/>
-        <v>81375</v>
-      </c>
-      <c r="BD6">
-        <f t="shared" si="1"/>
-        <v>63390</v>
-      </c>
-      <c r="BE6">
-        <f t="shared" si="1"/>
-        <v>65100</v>
-      </c>
-      <c r="BF6">
-        <f t="shared" si="1"/>
-        <v>78975</v>
-      </c>
-      <c r="BG6">
-        <f t="shared" si="1"/>
-        <v>3255</v>
-      </c>
-      <c r="BH6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BI6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BJ6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BK6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BL6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BM6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BN6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BO6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BP6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BQ6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BR6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BS6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BT6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BU6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BV6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BW6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BX6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BY6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BZ6">
-        <f t="shared" si="1"/>
-        <v>373072</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5210,7 +5005,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:AV56"/>
+  <dimension ref="A1:AU56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5221,8 +5016,7 @@
     <col min="10" max="10" width="7" customWidth="1"/>
     <col min="11" max="11" width="23" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="47" width="13" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="48" max="48" width="9.140625" collapsed="1"/>
+    <col min="13" max="47" width="13" customWidth="1" outlineLevel="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:47" x14ac:dyDescent="0.25">
@@ -5368,9 +5162,9 @@
         <v>224</v>
       </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>9500879389</v>
+    <row r="2" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>84</v>
       </c>
       <c r="B2">
         <v>202502</v>
@@ -5509,8 +5303,8 @@
       </c>
     </row>
     <row r="3" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>9500882917</v>
+      <c r="A3" t="s">
+        <v>85</v>
       </c>
       <c r="B3">
         <v>202502</v>
@@ -5648,9 +5442,9 @@
         <v>34040</v>
       </c>
     </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>9500879389</v>
+    <row r="4" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>84</v>
       </c>
       <c r="B4">
         <v>202502</v>
@@ -5789,8 +5583,8 @@
       </c>
     </row>
     <row r="5" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>9500882917</v>
+      <c r="A5" t="s">
+        <v>85</v>
       </c>
       <c r="B5">
         <v>202502</v>
@@ -5928,9 +5722,9 @@
         <v>62210</v>
       </c>
     </row>
-    <row r="6" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>9500879389</v>
+    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>84</v>
       </c>
       <c r="B6">
         <v>202503</v>
@@ -6069,8 +5863,8 @@
       </c>
     </row>
     <row r="7" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>9500882917</v>
+      <c r="A7" t="s">
+        <v>85</v>
       </c>
       <c r="B7">
         <v>202504</v>
@@ -6209,8 +6003,8 @@
       </c>
     </row>
     <row r="8" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>9500879389</v>
+      <c r="A8" t="s">
+        <v>84</v>
       </c>
       <c r="B8">
         <v>202504</v>
@@ -6349,8 +6143,8 @@
       </c>
     </row>
     <row r="9" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>9500882917</v>
+      <c r="A9" t="s">
+        <v>85</v>
       </c>
       <c r="B9">
         <v>202504</v>
@@ -6489,8 +6283,8 @@
       </c>
     </row>
     <row r="10" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9500882917</v>
+      <c r="A10" t="s">
+        <v>85</v>
       </c>
       <c r="B10">
         <v>202504</v>
@@ -6629,8 +6423,8 @@
       </c>
     </row>
     <row r="11" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>9500882917</v>
+      <c r="A11" t="s">
+        <v>85</v>
       </c>
       <c r="B11">
         <v>202504</v>
@@ -6769,8 +6563,8 @@
       </c>
     </row>
     <row r="12" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>9500882917</v>
+      <c r="A12" t="s">
+        <v>85</v>
       </c>
       <c r="B12">
         <v>202504</v>
@@ -6909,8 +6703,8 @@
       </c>
     </row>
     <row r="13" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>9500879389</v>
+      <c r="A13" t="s">
+        <v>84</v>
       </c>
       <c r="B13">
         <v>202504</v>
@@ -7049,8 +6843,8 @@
       </c>
     </row>
     <row r="14" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>9500879389</v>
+      <c r="A14" t="s">
+        <v>84</v>
       </c>
       <c r="B14">
         <v>202504</v>
@@ -7189,8 +6983,8 @@
       </c>
     </row>
     <row r="15" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>9500879389</v>
+      <c r="A15" t="s">
+        <v>84</v>
       </c>
       <c r="B15">
         <v>202503</v>
@@ -7329,8 +7123,8 @@
       </c>
     </row>
     <row r="16" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>9500879389</v>
+      <c r="A16" t="s">
+        <v>84</v>
       </c>
       <c r="B16">
         <v>202503</v>
@@ -7469,8 +7263,8 @@
       </c>
     </row>
     <row r="17" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>9500879389</v>
+      <c r="A17" t="s">
+        <v>84</v>
       </c>
       <c r="B17">
         <v>202503</v>
@@ -7609,8 +7403,8 @@
       </c>
     </row>
     <row r="18" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>9500879389</v>
+      <c r="A18" t="s">
+        <v>84</v>
       </c>
       <c r="B18">
         <v>202503</v>
@@ -7749,8 +7543,8 @@
       </c>
     </row>
     <row r="19" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>9500879389</v>
+      <c r="A19" t="s">
+        <v>84</v>
       </c>
       <c r="B19">
         <v>202503</v>
@@ -7889,8 +7683,8 @@
       </c>
     </row>
     <row r="20" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>9500879389</v>
+      <c r="A20" t="s">
+        <v>84</v>
       </c>
       <c r="B20">
         <v>202503</v>
@@ -8029,8 +7823,8 @@
       </c>
     </row>
     <row r="21" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>9500882917</v>
+      <c r="A21" t="s">
+        <v>85</v>
       </c>
       <c r="B21">
         <v>202503</v>
@@ -8169,8 +7963,8 @@
       </c>
     </row>
     <row r="22" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>9500882917</v>
+      <c r="A22" t="s">
+        <v>85</v>
       </c>
       <c r="B22">
         <v>202503</v>
@@ -8309,8 +8103,8 @@
       </c>
     </row>
     <row r="23" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>9500882917</v>
+      <c r="A23" t="s">
+        <v>85</v>
       </c>
       <c r="B23">
         <v>202503</v>
@@ -8449,8 +8243,8 @@
       </c>
     </row>
     <row r="24" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>9500879389</v>
+      <c r="A24" t="s">
+        <v>84</v>
       </c>
       <c r="B24">
         <v>202505</v>
@@ -8589,8 +8383,8 @@
       </c>
     </row>
     <row r="25" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>9500882917</v>
+      <c r="A25" t="s">
+        <v>85</v>
       </c>
       <c r="B25">
         <v>202505</v>
@@ -8729,8 +8523,8 @@
       </c>
     </row>
     <row r="26" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>9500879389</v>
+      <c r="A26" t="s">
+        <v>84</v>
       </c>
       <c r="B26">
         <v>202505</v>
@@ -8869,8 +8663,8 @@
       </c>
     </row>
     <row r="27" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>9500882917</v>
+      <c r="A27" t="s">
+        <v>85</v>
       </c>
       <c r="B27">
         <v>202505</v>
@@ -9009,8 +8803,8 @@
       </c>
     </row>
     <row r="28" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>9500882917</v>
+      <c r="A28" t="s">
+        <v>85</v>
       </c>
       <c r="B28">
         <v>202505</v>
@@ -9149,8 +8943,8 @@
       </c>
     </row>
     <row r="29" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>9500882917</v>
+      <c r="A29" t="s">
+        <v>85</v>
       </c>
       <c r="B29">
         <v>202505</v>
@@ -9289,8 +9083,8 @@
       </c>
     </row>
     <row r="30" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>9500882917</v>
+      <c r="A30" t="s">
+        <v>85</v>
       </c>
       <c r="B30">
         <v>202505</v>
@@ -9429,8 +9223,8 @@
       </c>
     </row>
     <row r="31" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>9500879389</v>
+      <c r="A31" t="s">
+        <v>84</v>
       </c>
       <c r="B31">
         <v>202505</v>
@@ -9569,8 +9363,8 @@
       </c>
     </row>
     <row r="32" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>9500879389</v>
+      <c r="A32" t="s">
+        <v>84</v>
       </c>
       <c r="B32">
         <v>202505</v>
@@ -9709,8 +9503,8 @@
       </c>
     </row>
     <row r="33" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>9500879389</v>
+      <c r="A33" t="s">
+        <v>84</v>
       </c>
       <c r="B33">
         <v>202505</v>
@@ -9849,8 +9643,8 @@
       </c>
     </row>
     <row r="34" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>9500882917</v>
+      <c r="A34" t="s">
+        <v>85</v>
       </c>
       <c r="B34">
         <v>202506</v>
@@ -9989,8 +9783,8 @@
       </c>
     </row>
     <row r="35" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>9500882917</v>
+      <c r="A35" t="s">
+        <v>85</v>
       </c>
       <c r="B35">
         <v>202506</v>
@@ -10129,8 +9923,8 @@
       </c>
     </row>
     <row r="36" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>9500882917</v>
+      <c r="A36" t="s">
+        <v>85</v>
       </c>
       <c r="B36">
         <v>202506</v>
@@ -10269,8 +10063,8 @@
       </c>
     </row>
     <row r="37" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>9500879389</v>
+      <c r="A37" t="s">
+        <v>84</v>
       </c>
       <c r="B37">
         <v>202506</v>
@@ -10409,8 +10203,8 @@
       </c>
     </row>
     <row r="38" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>9500882917</v>
+      <c r="A38" t="s">
+        <v>85</v>
       </c>
       <c r="B38">
         <v>202506</v>
@@ -10549,8 +10343,8 @@
       </c>
     </row>
     <row r="39" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>9500882917</v>
+      <c r="A39" t="s">
+        <v>85</v>
       </c>
       <c r="B39">
         <v>202506</v>
@@ -10689,8 +10483,8 @@
       </c>
     </row>
     <row r="40" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>9500882917</v>
+      <c r="A40" t="s">
+        <v>85</v>
       </c>
       <c r="B40">
         <v>202506</v>
@@ -10829,8 +10623,8 @@
       </c>
     </row>
     <row r="41" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>9500879389</v>
+      <c r="A41" t="s">
+        <v>84</v>
       </c>
       <c r="B41">
         <v>202506</v>
@@ -10969,8 +10763,8 @@
       </c>
     </row>
     <row r="42" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>9500879389</v>
+      <c r="A42" t="s">
+        <v>84</v>
       </c>
       <c r="B42">
         <v>202506</v>
@@ -11109,8 +10903,8 @@
       </c>
     </row>
     <row r="43" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>9500882917</v>
+      <c r="A43" t="s">
+        <v>85</v>
       </c>
       <c r="B43">
         <v>202509</v>
@@ -11249,8 +11043,8 @@
       </c>
     </row>
     <row r="44" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>9500882917</v>
+      <c r="A44" t="s">
+        <v>85</v>
       </c>
       <c r="B44">
         <v>202509</v>
@@ -11389,8 +11183,8 @@
       </c>
     </row>
     <row r="45" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>9500879389</v>
+      <c r="A45" t="s">
+        <v>84</v>
       </c>
       <c r="B45">
         <v>202509</v>
@@ -11529,8 +11323,8 @@
       </c>
     </row>
     <row r="46" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>9500879389</v>
+      <c r="A46" t="s">
+        <v>84</v>
       </c>
       <c r="B46">
         <v>202509</v>
@@ -11669,8 +11463,8 @@
       </c>
     </row>
     <row r="47" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>9500879389</v>
+      <c r="A47" t="s">
+        <v>84</v>
       </c>
       <c r="B47">
         <v>202508</v>
@@ -11809,8 +11603,8 @@
       </c>
     </row>
     <row r="48" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>9500882917</v>
+      <c r="A48" t="s">
+        <v>85</v>
       </c>
       <c r="B48">
         <v>202508</v>
@@ -11949,8 +11743,8 @@
       </c>
     </row>
     <row r="49" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>9500879389</v>
+      <c r="A49" t="s">
+        <v>84</v>
       </c>
       <c r="B49">
         <v>202508</v>
@@ -12089,8 +11883,8 @@
       </c>
     </row>
     <row r="50" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>9500879389</v>
+      <c r="A50" t="s">
+        <v>84</v>
       </c>
       <c r="B50">
         <v>202508</v>
@@ -12229,8 +12023,8 @@
       </c>
     </row>
     <row r="51" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>9500882917</v>
+      <c r="A51" t="s">
+        <v>85</v>
       </c>
       <c r="B51">
         <v>202507</v>
@@ -12369,8 +12163,8 @@
       </c>
     </row>
     <row r="52" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>9500879389</v>
+      <c r="A52" t="s">
+        <v>84</v>
       </c>
       <c r="B52">
         <v>202507</v>
@@ -12509,8 +12303,8 @@
       </c>
     </row>
     <row r="53" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>9500882917</v>
+      <c r="A53" t="s">
+        <v>85</v>
       </c>
       <c r="B53">
         <v>202507</v>
@@ -12649,8 +12443,8 @@
       </c>
     </row>
     <row r="54" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>9500882917</v>
+      <c r="A54" t="s">
+        <v>85</v>
       </c>
       <c r="B54">
         <v>202507</v>
@@ -12789,8 +12583,8 @@
       </c>
     </row>
     <row r="55" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>9500879389</v>
+      <c r="A55" t="s">
+        <v>84</v>
       </c>
       <c r="B55">
         <v>202507</v>
@@ -12929,8 +12723,8 @@
       </c>
     </row>
     <row r="56" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>9500879389</v>
+      <c r="A56" t="s">
+        <v>84</v>
       </c>
       <c r="B56">
         <v>202507</v>
@@ -13069,7 +12863,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L56" xr:uid="{00000000-0009-0000-0000-000002000000}">
+  <autoFilter ref="A1:AU56" xr:uid="{00000000-0009-0000-0000-000002000000}">
     <filterColumn colId="0">
       <filters>
         <filter val="9500879389"/>
@@ -13077,7 +12871,12 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="202502"/>
+        <filter val="202503"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="11">
+      <filters>
+        <filter val="Accrual"/>
       </filters>
     </filterColumn>
   </autoFilter>
